--- a/data/trans_orig/AIRE_2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Edad-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16619</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10114</t>
+          <t>10478</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20431</t>
+          <t>19976</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>47,99%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>13416</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>385</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>16796</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>19401</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>17511</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>31224</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29111</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47051</t>
+          <t>46652</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21254</t>
+          <t>21112</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33735</t>
+          <t>33487</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>18499</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42525</t>
+          <t>43099</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61258</t>
+          <t>60999</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>16668</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>9316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21628</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13158</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23335</t>
+          <t>23064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,47 +2144,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>17,03%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>9255</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>4793</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>16901</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>6,66%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>3,45%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>15,85%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>9255</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>4989</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>16911</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>6,66%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>8759</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24336</t>
+          <t>23498</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>14765</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30747</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27300</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48893</t>
+          <t>47507</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12562</t>
+          <t>12752</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24827</t>
+          <t>24850</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24051</t>
+          <t>23806</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39992</t>
+          <t>40588</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39896</t>
+          <t>41062</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60211</t>
+          <t>61228</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8744</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>20424</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>21577</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20405</t>
+          <t>19513</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39267</t>
+          <t>37038</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>12185</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>13858</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22637</t>
+          <t>22960</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>14613</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23115</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>16496</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80703</t>
+          <t>78982</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13304</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28555</t>
+          <t>29128</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>36482</t>
+          <t>36954</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>117592</t>
+          <t>123606</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>55,98%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19139</t>
+          <t>18883</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56881</t>
+          <t>56594</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42855</t>
+          <t>42650</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61997</t>
+          <t>62817</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>61995</t>
+          <t>57454</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>112611</t>
+          <t>110445</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,02%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26433</t>
+          <t>27023</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17702</t>
+          <t>17819</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41195</t>
+          <t>40553</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21323</t>
+          <t>21729</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15165</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>13804</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31882</t>
+          <t>32108</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>9154</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>24443</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13180</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29865</t>
+          <t>29446</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48235</t>
+          <t>46620</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50871</t>
+          <t>51338</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138388</t>
+          <t>142413</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58080</t>
+          <t>58500</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>84479</t>
+          <t>85366</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>119905</t>
+          <t>121665</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>213505</t>
+          <t>210906</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>63966</t>
+          <t>60260</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>112771</t>
+          <t>112187</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>100414</t>
+          <t>101797</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>130137</t>
+          <t>129402</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>179111</t>
+          <t>172806</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>236039</t>
+          <t>230690</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22935</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45156</t>
+          <t>45198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>36028</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>58322</t>
+          <t>57106</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>63763</t>
+          <t>64375</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>96098</t>
+          <t>96832</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>39998</t>
+          <t>40142</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20084</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>46140</t>
+          <t>45025</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>73063</t>
+          <t>73119</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>706</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>851</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>407</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3782</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1933</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6336</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27,08%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,37%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6898</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4084</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10583</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>29,01%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>44,5%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>9269</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11654</t>
+          <t>9635</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>14001</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,58%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5521</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8317</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>39,54%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>23,86%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>59,56%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8164</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5160</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11567</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>34,33%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>21,7%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>48,64%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7273</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>15113</t>
+          <t>12794</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19976</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>49,14%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2976</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5521</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21,31%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>39,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5735</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2959</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9283</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,44%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>39,04%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>12193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2493</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2255</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>803</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4821</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>23780</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>23780</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>23780</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>41623</t>
+          <t>35374</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>41623</t>
+          <t>35374</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>41623</t>
+          <t>35374</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4892</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2242</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4676</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1804</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9106</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16796</t>
+          <t>15003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19877</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14120</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26035</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,93%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>13457</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8576</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19401</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>23,39%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>33,73%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23843</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17511</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31224</t>
+          <t>14771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>37301</t>
+          <t>29967</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28251</t>
+          <t>22403</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46652</t>
+          <t>38021</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21717</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15862</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28237</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>34,14%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>24,94%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>44,39%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>27388</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>21112</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>33487</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>47,61%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>36,7%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>58,22%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24699</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18499</t>
+          <t>20879</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>31692</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>52088</t>
+          <t>47744</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43099</t>
+          <t>39762</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60999</t>
+          <t>56626</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>49,35%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9406</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15054</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,67%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4661</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2272</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8883</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>13819</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21513</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4354</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12546</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7340</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3896</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12893</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12,76%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>14001</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23064</t>
+          <t>21380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>63608</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>63608</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>63608</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>57523</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>57523</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>57523</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73546</t>
+          <t>51143</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>73546</t>
+          <t>51143</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73546</t>
+          <t>51143</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>131069</t>
+          <t>114751</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131069</t>
+          <t>114751</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>131069</t>
+          <t>114751</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6409</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2495</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12239</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2446</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6778</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
+          <t>2582</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
           <t>6808</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3320</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14054</t>
-        </is>
-      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,17 +2159,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19946</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13051</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>27333</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25,13%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>16,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>14746</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>8759</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>23498</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22313</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>7470</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31026</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>37059</t>
+          <t>32529</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27125</t>
+          <t>23977</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47507</t>
+          <t>41677</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30336</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>22493</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>38043</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>38,22%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>28,34%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>47,93%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>18449</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>12752</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>24850</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>32,69%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>22,6%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>44,04%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>31366</t>
+          <t>18808</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23806</t>
+          <t>13579</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40588</t>
+          <t>25739</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>49815</t>
+          <t>49143</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41062</t>
+          <t>39256</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61228</t>
+          <t>59089</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14534</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>22793</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18,31%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>28,72%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>13751</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>8563</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>20424</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>15,17%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>36,19%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13849</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>27601</t>
+          <t>28659</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19513</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37038</t>
+          <t>38977</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8140</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3717</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>13765</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>10,26%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>17,34%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>7037</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3581</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>12185</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>21,59%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13858</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>15745</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>23365</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>79364</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>79364</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>79364</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>56430</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>56430</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>56430</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>82506</t>
+          <t>55704</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>82506</t>
+          <t>55704</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82506</t>
+          <t>55704</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>138936</t>
+          <t>135067</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>138936</t>
+          <t>135067</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>138936</t>
+          <t>135067</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2631</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>13137</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>12,82%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>7930</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2948</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>14613</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13589</t>
+          <t>15369</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22145</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>18807</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>12428</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>26685</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>18,35%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>12,13%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>41567</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>16496</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>78982</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>36,33%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>14,42%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>69,04%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>18055</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29128</t>
+          <t>27007</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>61625</t>
+          <t>36862</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>36954</t>
+          <t>27161</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>123606</t>
+          <t>48243</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>49020</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>39517</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>59283</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>47,83%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>38,56%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>57,84%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>40587</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>18883</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>56594</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>35,48%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>16,51%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>49,47%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>52324</t>
+          <t>39846</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42650</t>
+          <t>32201</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>62817</t>
+          <t>48899</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>92911</t>
+          <t>88866</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>57454</t>
+          <t>76733</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>110445</t>
+          <t>101189</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>19600</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>12493</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>28300</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>19,12%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>12,19%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>27,61%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>10674</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>4030</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>17701</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11816</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27023</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>29471</t>
+          <t>30785</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17819</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40553</t>
+          <t>40700</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>9186</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>4547</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>15592</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>15,21%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>13649</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>5705</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>21729</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>11,93%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>18,99%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>20380</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>22597</t>
+          <t>23463</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13804</t>
+          <t>16296</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32108</t>
+          <t>32422</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>102493</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>102493</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>102493</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>114406</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>114406</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>114406</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>106378</t>
+          <t>91863</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>106378</t>
+          <t>91863</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106378</t>
+          <t>91863</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>220784</t>
+          <t>194356</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>220784</t>
+          <t>194356</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>220784</t>
+          <t>194356</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>11365</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>26633</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>15781</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>9154</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>24443</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29446</t>
+          <t>24564</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>35632</t>
+          <t>34148</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>24846</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46620</t>
+          <t>45405</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>62411</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>51807</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>75490</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>19,97%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>76668</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>51338</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>142413</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>30,41%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>20,36%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>56,48%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>70971</t>
+          <t>46581</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58500</t>
+          <t>37123</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>85366</t>
+          <t>57781</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>147639</t>
+          <t>108992</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>121665</t>
+          <t>93544</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>210906</t>
+          <t>126008</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>106593</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>91276</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>120418</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>35,18%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>46,42%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>94588</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>60260</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>112187</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>37,51%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>44,49%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>115337</t>
+          <t>91955</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>101797</t>
+          <t>80074</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>129402</t>
+          <t>104040</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>209926</t>
+          <t>198547</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>172806</t>
+          <t>180456</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>230690</t>
+          <t>216630</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -3787,67 +3787,67 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>46515</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>35486</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>58749</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>34821</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>23898</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>45198</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>13,81%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>17,93%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>46232</t>
+          <t>35066</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>35108</t>
+          <t>26868</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>57106</t>
+          <t>44866</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>81054</t>
+          <t>81581</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>64375</t>
+          <t>68910</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>96832</t>
+          <t>96798</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>26023</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>18805</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>35751</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>30281</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>20236</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>40142</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>12,01%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>15,92%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>30258</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>22842</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>39824</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>58162</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>45025</t>
+          <t>45226</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>73119</t>
+          <t>69207</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>259429</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>259429</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>259429</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>344</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>252140</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>252140</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>252140</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>280272</t>
+          <t>220120</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>280272</t>
+          <t>220120</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>280272</t>
+          <t>220120</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>532412</t>
+          <t>479549</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>532412</t>
+          <t>479549</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>532412</t>
+          <t>479549</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
